--- a/data_input/maiz_soil_params_irr_high.xlsx
+++ b/data_input/maiz_soil_params_irr_high.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\PyAEZ\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BF3DC5-0609-4D22-8209-6892943E5E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD6EC83-A1DA-4B3D-9600-7E969E8D32F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="6" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
   </bookViews>
   <sheets>
     <sheet name="SQ1" sheetId="1" r:id="rId1"/>
@@ -1046,22 +1046,22 @@
         <v>10</v>
       </c>
       <c r="B1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C1">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="D1">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E1">
         <v>35</v>
       </c>
       <c r="F1">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G1">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1069,22 +1069,22 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
       <c r="F2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1656,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="C1">
+        <v>10</v>
+      </c>
+      <c r="D1">
         <v>20</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>35</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>70</v>
       </c>
-      <c r="F1">
-        <v>85</v>
-      </c>
       <c r="G1">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
